--- a/DIAGRAMA GANTT.xlsx
+++ b/DIAGRAMA GANTT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Documents\GitHub\Strategic-Thinking-SEP-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D710F814-4AED-4310-812A-9FC98CDB7523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3D7D9E-2E8E-4C70-90A2-D3F0851FB47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F9D96E2-D5D0-44B9-B419-1F0B0964B7F7}"/>
   </bookViews>
@@ -290,66 +290,78 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -358,25 +370,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -400,23 +397,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>244955</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>29736</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>304803</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>397355</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>151656</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>457203</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>243840</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Diamond 3">
+        <xdr:cNvPr id="5" name="Diamond 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C97E4C7-32CC-4FFA-BCCC-7E10BACAB1AC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{002FF6A1-206E-449B-80AC-55D09E6E8285}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -424,7 +421,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12827248" y="5122126"/>
+          <a:off x="10628974" y="4182822"/>
           <a:ext cx="152400" cy="121920"/>
         </a:xfrm>
         <a:prstGeom prst="diamond">
@@ -462,22 +459,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>304803</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:colOff>334537</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>46464</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>457203</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>243840</xdr:rowOff>
+      <xdr:colOff>486937</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>168384</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Diamond 4">
+        <xdr:cNvPr id="2" name="Diamond 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{002FF6A1-206E-449B-80AC-55D09E6E8285}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2922D537-69F0-41DA-AA85-8970833B8058}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -485,7 +482,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10628974" y="4182822"/>
+          <a:off x="11541513" y="5203903"/>
           <a:ext cx="152400" cy="121920"/>
         </a:xfrm>
         <a:prstGeom prst="diamond">
@@ -843,29 +840,29 @@
   <dimension ref="H1:Q23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="46" style="28" customWidth="1"/>
+    <col min="8" max="8" width="46" style="23" customWidth="1"/>
     <col min="9" max="16" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="8:17" ht="15.6" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="8:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="31"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="8:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="H3" s="24"/>
+      <c r="H3" s="28"/>
       <c r="I3" s="2">
         <v>46296</v>
       </c>
@@ -895,7 +892,7 @@
       </c>
     </row>
     <row r="4" spans="8:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4"/>
@@ -909,7 +906,7 @@
       <c r="Q4" s="6"/>
     </row>
     <row r="5" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="7"/>
@@ -923,175 +920,114 @@
       <c r="Q5" s="6"/>
     </row>
     <row r="6" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="21" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
       <c r="Q6" s="6"/>
     </row>
     <row r="7" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="21" t="s">
         <v>6</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
       <c r="Q7" s="6"/>
     </row>
     <row r="8" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="6"/>
     </row>
     <row r="9" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+      <c r="I9" s="10"/>
       <c r="Q9" s="6"/>
     </row>
     <row r="10" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
       <c r="Q10" s="6"/>
     </row>
     <row r="11" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="K11" s="10"/>
+      <c r="M11" s="10"/>
       <c r="Q11" s="6"/>
     </row>
     <row r="12" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
+      <c r="M12" s="10"/>
       <c r="Q12" s="6"/>
     </row>
     <row r="13" spans="8:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="24" t="s">
         <v>10</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="21"/>
+      <c r="L13" s="5"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="12"/>
+      <c r="Q13" s="11"/>
     </row>
     <row r="14" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="20" t="s">
         <v>13</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="6"/>
     </row>
     <row r="15" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
       <c r="Q15" s="6"/>
     </row>
     <row r="16" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
+      <c r="N16" s="13"/>
       <c r="Q16" s="6"/>
     </row>
     <row r="17" spans="8:17" ht="30" x14ac:dyDescent="0.3">
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
       <c r="Q17" s="6"/>
     </row>
     <row r="18" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H18" s="25" t="s">
+      <c r="H18" s="20" t="s">
         <v>14</v>
       </c>
       <c r="I18" s="5"/>
@@ -1099,41 +1035,29 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="15"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="29"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="6"/>
     </row>
     <row r="19" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H19" s="26" t="s">
+      <c r="H19" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="9"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="30"/>
       <c r="Q19" s="6"/>
     </row>
     <row r="20" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H20" s="26" t="s">
+      <c r="H20" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="9"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="30"/>
       <c r="Q20" s="6"/>
     </row>
     <row r="21" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="20" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="5"/>
@@ -1141,38 +1065,32 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
+      <c r="N21" s="16"/>
       <c r="O21" s="5"/>
-      <c r="P21" s="17"/>
+      <c r="P21" s="29"/>
       <c r="Q21" s="6"/>
     </row>
     <row r="22" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H22" s="26" t="s">
+      <c r="H22" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="18"/>
+      <c r="N22" s="17"/>
+      <c r="P22" s="30"/>
       <c r="Q22" s="6"/>
     </row>
     <row r="23" spans="8:17" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H23" s="27" t="s">
+      <c r="H23" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="20"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/DIAGRAMA GANTT.xlsx
+++ b/DIAGRAMA GANTT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Documents\GitHub\Strategic-Thinking-SEP-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3D7D9E-2E8E-4C70-90A2-D3F0851FB47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC4DE5D-52B3-44BE-A6DF-65C64461AE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F9D96E2-D5D0-44B9-B419-1F0B0964B7F7}"/>
   </bookViews>
@@ -290,37 +290,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -333,30 +358,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -369,12 +378,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,23 +461,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>334537</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>306659</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>46464</xdr:rowOff>
+      <xdr:rowOff>37171</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>486937</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>459059</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>168384</xdr:rowOff>
+      <xdr:rowOff>159091</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Diamond 1">
+        <xdr:cNvPr id="3" name="Diamond 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2922D537-69F0-41DA-AA85-8970833B8058}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14CB30AF-ECA2-4E65-B75F-936891C39139}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -482,7 +485,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11541513" y="5203903"/>
+          <a:off x="12266342" y="5194610"/>
           <a:ext cx="152400" cy="121920"/>
         </a:xfrm>
         <a:prstGeom prst="diamond">
@@ -837,264 +840,236 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0000DF-CA16-4C22-847A-A462A509DCE9}">
-  <dimension ref="H1:Q23"/>
+  <dimension ref="H1:O23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="46" style="23" customWidth="1"/>
-    <col min="9" max="16" width="11" style="1" customWidth="1"/>
+    <col min="8" max="8" width="46" style="7" customWidth="1"/>
+    <col min="9" max="15" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:17" ht="15.6" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="8:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="H2" s="27" t="s">
+    <row r="1" spans="8:15" ht="15.6" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="8:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="26"/>
-    </row>
-    <row r="3" spans="8:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="H3" s="28"/>
-      <c r="I3" s="2">
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="27"/>
+    </row>
+    <row r="3" spans="8:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H3" s="29"/>
+      <c r="I3" s="9">
         <v>46296</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="9">
         <v>46327</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="9">
         <v>46357</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="9">
         <v>46388</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="9">
         <v>46419</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="9">
         <v>46447</v>
       </c>
       <c r="O3" s="2">
         <v>46478</v>
       </c>
-      <c r="P3" s="2">
-        <v>46508</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>46539</v>
-      </c>
-    </row>
-    <row r="4" spans="8:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="H4" s="24" t="s">
+    </row>
+    <row r="4" spans="8:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="6"/>
-    </row>
-    <row r="5" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H5" s="20" t="s">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="12"/>
+    </row>
+    <row r="5" spans="8:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="6"/>
-    </row>
-    <row r="6" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H6" s="21" t="s">
+      <c r="I5" s="13"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="Q6" s="6"/>
-    </row>
-    <row r="7" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H7" s="21" t="s">
+      <c r="I6" s="14"/>
+      <c r="O6" s="15"/>
+    </row>
+    <row r="7" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="Q7" s="6"/>
-    </row>
-    <row r="8" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H8" s="20" t="s">
+      <c r="I7" s="14"/>
+      <c r="O7" s="15"/>
+    </row>
+    <row r="8" spans="8:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="6"/>
-    </row>
-    <row r="9" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H9" s="21" t="s">
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12"/>
+    </row>
+    <row r="9" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="Q9" s="6"/>
-    </row>
-    <row r="10" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H10" s="21" t="s">
+      <c r="I9" s="17"/>
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H10" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="Q10" s="6"/>
-    </row>
-    <row r="11" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H11" s="21" t="s">
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="O10" s="15"/>
+    </row>
+    <row r="11" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="Q11" s="6"/>
-    </row>
-    <row r="12" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H12" s="21" t="s">
+      <c r="K11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="O11" s="15"/>
+    </row>
+    <row r="12" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M12" s="10"/>
-      <c r="Q12" s="6"/>
-    </row>
-    <row r="13" spans="8:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="H13" s="24" t="s">
+      <c r="M12" s="17"/>
+      <c r="O12" s="15"/>
+    </row>
+    <row r="13" spans="8:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="11"/>
-    </row>
-    <row r="14" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H14" s="20" t="s">
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="18"/>
+    </row>
+    <row r="14" spans="8:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="6"/>
-    </row>
-    <row r="15" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H15" s="21" t="s">
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="12"/>
+    </row>
+    <row r="15" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="Q15" s="6"/>
-    </row>
-    <row r="16" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H16" s="21" t="s">
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="15"/>
+    </row>
+    <row r="16" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="N16" s="13"/>
-      <c r="Q16" s="6"/>
-    </row>
-    <row r="17" spans="8:17" ht="30" x14ac:dyDescent="0.3">
-      <c r="H17" s="21" t="s">
+      <c r="N16" s="20"/>
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" spans="8:15" ht="30" x14ac:dyDescent="0.3">
+      <c r="H17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="Q17" s="6"/>
-    </row>
-    <row r="18" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H18" s="20" t="s">
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="8:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="6"/>
-    </row>
-    <row r="19" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H19" s="21" t="s">
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="12"/>
+    </row>
+    <row r="19" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="30"/>
-      <c r="Q19" s="6"/>
-    </row>
-    <row r="20" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H20" s="21" t="s">
+      <c r="N19" s="22"/>
+      <c r="O19" s="15"/>
+    </row>
+    <row r="20" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="N20" s="15"/>
-      <c r="O20" s="30"/>
-      <c r="Q20" s="6"/>
-    </row>
-    <row r="21" spans="8:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H21" s="20" t="s">
+      <c r="N20" s="22"/>
+      <c r="O20" s="15"/>
+    </row>
+    <row r="21" spans="8:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="6"/>
-    </row>
-    <row r="22" spans="8:17" x14ac:dyDescent="0.3">
-      <c r="H22" s="21" t="s">
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="23"/>
+    </row>
+    <row r="22" spans="8:15" x14ac:dyDescent="0.3">
+      <c r="H22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N22" s="17"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="6"/>
-    </row>
-    <row r="23" spans="8:17" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H23" s="22" t="s">
+      <c r="O22" s="24"/>
+    </row>
+    <row r="23" spans="8:15" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="19"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="I2:Q2"/>
+    <mergeCell ref="I2:O2"/>
     <mergeCell ref="H2:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
